--- a/EXCEL/Exercise Files/Chapter01/Chapter_1_Challenge.xlsx
+++ b/EXCEL/Exercise Files/Chapter01/Chapter_1_Challenge.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22FA4BC-8689-44E0-A184-06BC9F77EE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A62DC9-63B8-4160-A808-AA0C0683E253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{67F2E7B7-3773-4320-B1D1-CC76282B8E2C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{67F2E7B7-3773-4320-B1D1-CC76282B8E2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -78,8 +77,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -157,20 +156,20 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -489,19 +488,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D84C4B-74A5-40C3-A5A0-2686DA343E95}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.84375" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.15" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -512,7 +511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -520,7 +519,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -530,9 +529,12 @@
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E5" s="6">
+        <f>AVERAGE(B4:B33)</f>
+        <v>1319.4666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -542,9 +544,12 @@
       <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E6" s="6">
+        <f>MEDIAN(B4:B34)</f>
+        <v>1285.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -553,7 +558,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -563,9 +568,12 @@
       <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E8" s="6">
+        <f>MAX(B4:B33)</f>
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -575,9 +583,12 @@
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E9" s="6">
+        <f>MIN(B4:B33)</f>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -587,9 +598,12 @@
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E10" s="6">
+        <f>_xlfn.QUARTILE.EXC(B4:B33,1)</f>
+        <v>1072.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -599,9 +613,12 @@
       <c r="D11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E11" s="6">
+        <f>_xlfn.QUARTILE.EXC(B4:B33,3)</f>
+        <v>1569.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -610,7 +627,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -620,9 +637,12 @@
       <c r="D13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E13" s="2">
+        <f>_xlfn.VAR.S(B4:B33)</f>
+        <v>249270.60229885063</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -632,9 +652,12 @@
       <c r="D14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E14" s="2">
+        <f>_xlfn.STDEV.S(B4:B33)</f>
+        <v>499.27006950031625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -642,7 +665,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -650,7 +673,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -658,7 +681,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -666,7 +689,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -674,7 +697,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>17</v>
       </c>
@@ -682,7 +705,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -690,7 +713,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
@@ -698,7 +721,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -706,7 +729,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>21</v>
       </c>
@@ -714,7 +737,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>22</v>
       </c>
@@ -722,7 +745,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>23</v>
       </c>
@@ -730,7 +753,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>24</v>
       </c>
@@ -738,7 +761,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25</v>
       </c>
@@ -746,7 +769,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26</v>
       </c>
@@ -754,7 +777,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>27</v>
       </c>
@@ -762,7 +785,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>28</v>
       </c>
@@ -770,7 +793,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>29</v>
       </c>
@@ -778,7 +801,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>30</v>
       </c>
